--- a/survey_templates/042_smartphone_use_and_productivity_survey--survey_templates.xlsx
+++ b/survey_templates/042_smartphone_use_and_productivity_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'always'}</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Always'}</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'most_of_the_time'}</t>
+          <t>most_of_the_time</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Most of the time'}</t>
+          <t>Most of the time</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Social Media'}</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'chat_apps'}</t>
+          <t>chat_apps</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Chat apps'}</t>
+          <t>Chat apps</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'videos'}</t>
+          <t>videos</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Videos'}</t>
+          <t>Videos</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Social media'}</t>
+          <t>Social media</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'gaming'}</t>
+          <t>gaming</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Gaming'}</t>
+          <t>Gaming</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'music'}</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Music'}</t>
+          <t>Music</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'improved_productivity'}</t>
+          <t>improved_productivity</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Improved productivity'}</t>
+          <t>Improved productivity</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'reduced_stress'}</t>
+          <t>reduced_stress</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Reduced stress'}</t>
+          <t>Reduced stress</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'improved_organization'}</t>
+          <t>improved_organization</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Improved organization'}</t>
+          <t>Improved organization</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'better_sleep'}</t>
+          <t>better_sleep</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Better sleep'}</t>
+          <t>Better sleep</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'social_isolation'}</t>
+          <t>social_isolation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Social isolation'}</t>
+          <t>Social isolation</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'eye_strain'}</t>
+          <t>eye_strain</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Eye strain'}</t>
+          <t>Eye strain</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'headaches'}</t>
+          <t>headaches</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Headaches'}</t>
+          <t>Headaches</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'sleep_disruptions'}</t>
+          <t>sleep_disruptions</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Sleep disruptions'}</t>
+          <t>Sleep disruptions</t>
         </is>
       </c>
     </row>
